--- a/d/2026-09-01_会员有效性分析.xlsx
+++ b/d/2026-09-01_会员有效性分析.xlsx
@@ -6407,12 +6407,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>nova 15 Ultra SLY-AL00（12GB+512GB）带感绿</t>
+          <t>nova 15 Ultra SLY-AL00（12GB+512GB）幻夜黑</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>6942103183102</t>
+          <t>6942103183133</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -6517,12 +6517,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>nova 15 Ultra SLY-AL00（12GB+512GB）幻夜黑</t>
+          <t>nova 15 Ultra SLY-AL00（12GB+512GB）带感绿</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6942103183133</t>
+          <t>6942103183102</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -8222,12 +8222,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -8387,12 +8387,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -8442,12 +8442,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -8497,12 +8497,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -8607,12 +8607,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -8662,12 +8662,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -8717,12 +8717,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -8772,12 +8772,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -9267,12 +9267,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K54" t="n">
@@ -9377,12 +9377,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K56" t="n">
@@ -9432,12 +9432,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K58" t="n">
@@ -9542,12 +9542,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K59" t="n">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -9762,12 +9762,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K63" t="n">
@@ -9817,12 +9817,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K64" t="n">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K66" t="n">
@@ -9982,12 +9982,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -10037,12 +10037,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K68" t="n">
@@ -10092,12 +10092,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K69" t="n">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K70" t="n">
@@ -10312,12 +10312,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K73" t="n">
@@ -10367,12 +10367,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K74" t="n">
@@ -10477,12 +10477,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K76" t="n">
@@ -10532,12 +10532,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -10587,12 +10587,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K78" t="n">
@@ -10642,12 +10642,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K79" t="n">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K81" t="n">
@@ -10807,12 +10807,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K83" t="n">
@@ -10972,12 +10972,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K85" t="n">
@@ -11082,12 +11082,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K88" t="n">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K90" t="n">
@@ -11302,12 +11302,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K91" t="n">
@@ -11357,12 +11357,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -11412,12 +11412,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K93" t="n">
@@ -11632,12 +11632,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -11742,12 +11742,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K99" t="n">
@@ -11797,12 +11797,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K100" t="n">
@@ -11852,12 +11852,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K101" t="n">
@@ -11907,12 +11907,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K102" t="n">
@@ -11962,12 +11962,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K103" t="n">
@@ -12017,12 +12017,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K104" t="n">
@@ -12072,12 +12072,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K105" t="n">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K106" t="n">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K107" t="n">
@@ -12292,12 +12292,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K109" t="n">
@@ -12402,12 +12402,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K111" t="n">
@@ -12567,12 +12567,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K114" t="n">
@@ -12622,12 +12622,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K115" t="n">
@@ -12677,12 +12677,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K116" t="n">
@@ -12732,12 +12732,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K117" t="n">
@@ -12787,12 +12787,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K118" t="n">
@@ -12897,12 +12897,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K120" t="n">
@@ -12952,12 +12952,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K121" t="n">
@@ -13062,12 +13062,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K123" t="n">
@@ -13117,12 +13117,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K124" t="n">
@@ -13227,12 +13227,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K126" t="n">
@@ -13282,12 +13282,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K127" t="n">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K128" t="n">
@@ -13392,12 +13392,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K129" t="n">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K130" t="n">
@@ -13502,12 +13502,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K131" t="n">
@@ -13557,12 +13557,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K132" t="n">
@@ -13722,12 +13722,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K135" t="n">
@@ -13777,12 +13777,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K136" t="n">
@@ -13832,12 +13832,12 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K137" t="n">
@@ -13887,12 +13887,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K138" t="n">
@@ -13942,12 +13942,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K139" t="n">
@@ -13997,12 +13997,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K140" t="n">
@@ -14052,12 +14052,12 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K141" t="n">
@@ -14162,12 +14162,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K143" t="n">
@@ -14217,12 +14217,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K144" t="n">
@@ -14272,12 +14272,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K145" t="n">
@@ -14327,12 +14327,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K146" t="n">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K148" t="n">
@@ -14492,12 +14492,12 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K149" t="n">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K150" t="n">
@@ -14602,12 +14602,12 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K151" t="n">
@@ -14657,12 +14657,12 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K152" t="n">
@@ -14712,12 +14712,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K153" t="n">
@@ -14822,12 +14822,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K155" t="n">
@@ -14877,12 +14877,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K156" t="n">
@@ -14932,12 +14932,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K157" t="n">
@@ -14987,12 +14987,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K158" t="n">
@@ -15097,12 +15097,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K160" t="n">
@@ -15262,12 +15262,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K163" t="n">
@@ -15317,12 +15317,12 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K164" t="n">
@@ -15372,12 +15372,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K165" t="n">
@@ -15482,12 +15482,12 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K167" t="n">
@@ -15647,12 +15647,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K170" t="n">
@@ -15922,12 +15922,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 雪域白</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>6942103152702</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K175" t="n">
@@ -15977,12 +15977,12 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 雪域白</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103152702</t>
         </is>
       </c>
       <c r="K176" t="n">
@@ -16032,12 +16032,12 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K177" t="n">
@@ -16087,12 +16087,12 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K178" t="n">
@@ -16307,12 +16307,12 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 雪域白</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152702</t>
         </is>
       </c>
       <c r="K182" t="n">
@@ -16362,12 +16362,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 雪域白</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>6942103152702</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K183" t="n">
@@ -16742,7 +16742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O77"/>
+  <dimension ref="A1:O78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16870,12 +16870,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MS16CC PD 240W 快充数据线 1.5m 太空银</t>
+          <t>MAXCO美能格 MC32 45W 双口氮化镓快充充电器 珍珠白</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>6955482539521</t>
+          <t>6955482537596</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -16941,12 +16941,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>MAXCO美能格 MC32 45W 双口氮化镓快充充电器 珍珠白</t>
+          <t>MAXCO美能格 MS16CC PD 240W 快充数据线 1.5m 太空银</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>6955482537596</t>
+          <t>6955482539521</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -17012,12 +17012,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Apple Watch Series 11 (GPS)；46 毫米玫瑰金色铝金属表壳；淡桃粉色运动型表带 - M/L - MEVU4CH/B</t>
+          <t>Apple Watch Series 11 (GPS)；46 毫米亮黑色铝金属表壳；黑色运动型表带 - M/L - MEVH4CH/B</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>195****64870</t>
+          <t>195****64757</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -17083,12 +17083,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Apple Watch Series 11 (GPS)；46 毫米亮黑色铝金属表壳；黑色运动型表带 - M/L - MEVH4CH/B</t>
+          <t>Apple Watch Series 11 (GPS)；46 毫米玫瑰金色铝金属表壳；淡桃粉色运动型表带 - M/L - MEVU4CH/B</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>195****64757</t>
+          <t>195****64870</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -17362,17 +17362,17 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 曜黑色</t>
+          <t>VOKAMO沃咔曼 iPhone 17&amp;17 Pro 钻石高清三强钢化玻璃膜 黑</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>6955482542736</t>
+          <t>6922329935921</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -17433,17 +17433,17 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPhone 17&amp;17 Pro 钻石高清三强钢化玻璃膜 黑</t>
+          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>6922329935921</t>
+          <t>6922329936560</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -17509,12 +17509,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
+          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 曜黑色</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>6922329936560</t>
+          <t>6955482542736</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -17788,17 +17788,17 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>耳机与扬声器</t>
+          <t>iPad Pro</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>RECCI锐思 REP W59 铂爵 ANC 头戴式无线耳机</t>
+          <t>11 英寸 iPad Pro 无线局域网机型 256GB 配标准玻璃面板 - 银色</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>6955482533109</t>
+          <t>195****95549</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -17859,17 +17859,17 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>耳机与扬声器</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>ZGA iPad 明派旋转系列保护皮套带笔槽</t>
+          <t>RECCI锐思 REP W59 铂爵 ANC 头戴式无线耳机</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>6927123805548</t>
+          <t>6955482533109</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -17930,17 +17930,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>iPad Pro</t>
+          <t>创意工具</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>11 英寸 iPad Pro 无线局域网机型 256GB 配标准玻璃面板 - 银色</t>
+          <t>VOKAMO沃咔曼 iLink Pencil 智联系列电容手写笔</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>195****95549</t>
+          <t>6922329934436</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -18072,17 +18072,17 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>创意工具</t>
+          <t>支架</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iLink Pencil 智联系列电容手写笔</t>
+          <t>RECCI锐思 RHO-M23 折叠旋转 iPad 支架</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>6922329934436</t>
+          <t>6955482542989</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -18143,17 +18143,17 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>支架</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>RECCI锐思 RHO-M23 折叠旋转 iPad 支架</t>
+          <t>ZGA iPad 明派旋转系列保护皮套带笔槽</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>6955482542989</t>
+          <t>6927123805548</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -18285,17 +18285,17 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>支架</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>UGREEN绿联 iPad 旋转折叠平板支架 银色</t>
+          <t>VOKAMO沃咔曼 iPad 系列魔幻旋转防刮保护套</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>6941876245338</t>
+          <t>6922329935303</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -18361,12 +18361,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPad 系列魔幻旋转防刮保护套</t>
+          <t>MOCOLL摩可 铂金系列 iPad 高清钢化膜 11 英寸 iPad (A16) 透明</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>6922329935303</t>
+          <t>6937045874478</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -18427,17 +18427,17 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>创意工具</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>MOCOLL摩可 铂金系列 iPad 高清钢化膜 11 英寸 iPad (A16) 透明</t>
+          <t>VOKAMO沃咔曼 iLink Pencil 智联系列电容手写笔</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>6937045874478</t>
+          <t>6922329934436</t>
         </is>
       </c>
       <c r="L24" t="n">
@@ -18498,17 +18498,17 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>创意工具</t>
+          <t>支架</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iLink Pencil 智联系列电容手写笔</t>
+          <t>UGREEN绿联 iPad 旋转折叠平板支架 银色</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>6922329934436</t>
+          <t>6941876245338</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -18711,17 +18711,17 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max</t>
+          <t>苹果电源</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max 512GB 深蓝色 - MG084CH/A</t>
+          <t>20W USB-C 电源适配器-MWVW3CH/A</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>195****41165</t>
+          <t>195****37103</t>
         </is>
       </c>
       <c r="L28" t="n">
@@ -18782,17 +18782,17 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>苹果电源</t>
+          <t>iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>20W USB-C 电源适配器-MWVW3CH/A</t>
+          <t>iPhone 17 Pro Max 512GB 深蓝色 - MG084CH/A</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>195****37103</t>
+          <t>195****41165</t>
         </is>
       </c>
       <c r="L29" t="n">
@@ -18929,12 +18929,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>MOPHIE摩尔菲 45W 氮化镓快充头</t>
+          <t>UGREEN绿联 USB-C PD 快充硅胶编织数据线 60W 1.5m</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>840390349200</t>
+          <t>6941876245444</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -19000,12 +19000,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>UGREEN绿联 USB-C PD 快充硅胶编织数据线 60W 1.5m</t>
+          <t>MOPHIE摩尔菲 45W 氮化镓快充头</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>6941876245444</t>
+          <t>840390349200</t>
         </is>
       </c>
       <c r="L32" t="n">
@@ -19142,12 +19142,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>MOMAX摩米士 iPhone 17 Pro Max 空气防摔磁吸保护壳 太阳橙</t>
+          <t>VOKAMO沃咔曼 iPhone 17系列 冰晶 AR 增透镜头保护膜 透明 三镜片</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>4894222083837</t>
+          <t>6922329936034</t>
         </is>
       </c>
       <c r="L34" t="n">
@@ -19279,17 +19279,17 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPhone 17系列 冰晶 AR 增透镜头保护膜 透明 三镜片</t>
+          <t>MOPHIE摩尔菲 45W 氮化镓快充头</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>6922329936034</t>
+          <t>840390349200</t>
         </is>
       </c>
       <c r="L36" t="n">
@@ -19350,17 +19350,17 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>MOPHIE摩尔菲 45W 氮化镓快充头</t>
+          <t>MOMAX摩米士 iPhone 17 Pro Max 空气防摔磁吸保护壳 太阳橙</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>840390349200</t>
+          <t>4894222083837</t>
         </is>
       </c>
       <c r="L37" t="n">
@@ -19421,17 +19421,17 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>FPV</t>
+          <t>购物袋</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>DJI Neo 2（仅飞行器）</t>
+          <t>DJI 无纺布购物袋（中号）</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>6937224131767</t>
+          <t>6937224129511</t>
         </is>
       </c>
       <c r="L38" t="n">
@@ -19492,17 +19492,17 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>购物袋</t>
+          <t>FPV</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>DJI 无纺布购物袋（中号）</t>
+          <t>DJI Neo 2（仅飞行器）</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>6937224129511</t>
+          <t>6937224131767</t>
         </is>
       </c>
       <c r="L39" t="n">
@@ -22001,7 +22001,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>华为北京旧宫万科</t>
+          <t>华为北京平谷万达</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -22011,7 +22011,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LSD2026090101099369</t>
+          <t>LSD2026090101102819</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -22031,22 +22031,22 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>+86-180****0250</t>
+          <t>+86-137****8759</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Watch GT系列</t>
+          <t>FreeClip</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>WATCH GT 7 NSU-B39 41mm(蓝色易扣氟橡胶表带)晴光蓝</t>
+          <t>FreeClip 2 耳夹耳机无线充 羽沙白</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>6942711307730</t>
+          <t>6942103169410</t>
         </is>
       </c>
       <c r="L75" t="n">
@@ -22056,7 +22056,7 @@
         <v>1</v>
       </c>
       <c r="N75" t="n">
-        <v>1588</v>
+        <v>1249</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -22072,7 +22072,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>华为北京西铁营万达</t>
+          <t>华为北京旧宫万科</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -22082,7 +22082,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LSD2026090101100943</t>
+          <t>LSD2026090101099369</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -22102,22 +22102,22 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>+86-186****2862</t>
+          <t>+86-180****0250</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>保护</t>
+          <t>Watch GT系列</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>三源 nova16Pro/Ultra/SE 2.5D 高清全屏钢化膜</t>
+          <t>WATCH GT 7 NSU-B39 41mm(蓝色易扣氟橡胶表带)晴光蓝</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>6979434901181</t>
+          <t>6942711307730</t>
         </is>
       </c>
       <c r="L76" t="n">
@@ -22127,7 +22127,7 @@
         <v>1</v>
       </c>
       <c r="N76" t="n">
-        <v>170</v>
+        <v>1588</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -22143,7 +22143,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>华为北京长楹龙湖</t>
+          <t>华为北京西铁营万达</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -22153,7 +22153,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LSD2026090101098948</t>
+          <t>LSD2026090101100943</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -22173,22 +22173,22 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>+86-188****1580</t>
+          <t>+86-186****2862</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Watch GT系列</t>
+          <t>保护</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>WATCH GT 7 NSU-B39 41mm(蓝色易扣氟橡胶表带)晴光蓝</t>
+          <t>三源 nova16Pro/Ultra/SE 2.5D 高清全屏钢化膜</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>6942711307730</t>
+          <t>6979434901181</t>
         </is>
       </c>
       <c r="L77" t="n">
@@ -22198,9 +22198,80 @@
         <v>1</v>
       </c>
       <c r="N77" t="n">
+        <v>170</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>北京易联</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>华为北京长楹龙湖</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>常规</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LSD2026090101098948</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>零售单</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>已退货</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>销售</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>+86-188****1580</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Watch GT系列</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>WATCH GT 7 NSU-B39 41mm(蓝色易扣氟橡胶表带)晴光蓝</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>6942711307730</t>
+        </is>
+      </c>
+      <c r="L78" t="n">
+        <v>1</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1</v>
+      </c>
+      <c r="N78" t="n">
         <v>1588</v>
       </c>
-      <c r="O77" t="inlineStr">
+      <c r="O78" t="inlineStr">
         <is>
           <t>北京易联</t>
         </is>

--- a/d/2026-09-01_会员有效性分析.xlsx
+++ b/d/2026-09-01_会员有效性分析.xlsx
@@ -6407,12 +6407,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>nova 15 Ultra SLY-AL00（12GB+512GB）幻夜黑</t>
+          <t>nova 15 Ultra SLY-AL00（12GB+512GB）带感绿</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>6942103183133</t>
+          <t>6942103183102</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -6517,12 +6517,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>nova 15 Ultra SLY-AL00（12GB+512GB）带感绿</t>
+          <t>nova 15 Ultra SLY-AL00（12GB+512GB）幻夜黑</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6942103183102</t>
+          <t>6942103183133</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -7122,12 +7122,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -7177,12 +7177,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -7342,12 +7342,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -7452,12 +7452,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -7672,12 +7672,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -7727,12 +7727,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -7837,12 +7837,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -8222,12 +8222,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -8387,12 +8387,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -8442,12 +8442,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -8497,12 +8497,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -8607,12 +8607,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -8662,12 +8662,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -8717,12 +8717,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -8772,12 +8772,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K52" t="n">
@@ -9267,12 +9267,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K54" t="n">
@@ -9377,12 +9377,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K56" t="n">
@@ -9432,12 +9432,12 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K57" t="n">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K58" t="n">
@@ -9542,12 +9542,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K59" t="n">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -9762,12 +9762,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K63" t="n">
@@ -9817,12 +9817,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K64" t="n">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K66" t="n">
@@ -9982,12 +9982,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -10037,12 +10037,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K68" t="n">
@@ -10092,12 +10092,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K69" t="n">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K70" t="n">
@@ -10312,12 +10312,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K73" t="n">
@@ -10367,12 +10367,12 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K74" t="n">
@@ -10477,12 +10477,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K76" t="n">
@@ -10532,12 +10532,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -10587,12 +10587,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K78" t="n">
@@ -10642,12 +10642,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K79" t="n">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K81" t="n">
@@ -10807,12 +10807,12 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K83" t="n">
@@ -10972,12 +10972,12 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K85" t="n">
@@ -11082,12 +11082,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K88" t="n">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K90" t="n">
@@ -11302,12 +11302,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K91" t="n">
@@ -11357,12 +11357,12 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K92" t="n">
@@ -11412,12 +11412,12 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K93" t="n">
@@ -11632,12 +11632,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K97" t="n">
@@ -11742,12 +11742,12 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K99" t="n">
@@ -11797,12 +11797,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K100" t="n">
@@ -11852,12 +11852,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K101" t="n">
@@ -11907,12 +11907,12 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K102" t="n">
@@ -11962,12 +11962,12 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K103" t="n">
@@ -12017,12 +12017,12 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K104" t="n">
@@ -12072,12 +12072,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K105" t="n">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K106" t="n">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K107" t="n">
@@ -12292,12 +12292,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K109" t="n">
@@ -12402,12 +12402,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K111" t="n">
@@ -12567,12 +12567,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K114" t="n">
@@ -12622,12 +12622,12 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K115" t="n">
@@ -12677,12 +12677,12 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K116" t="n">
@@ -12732,12 +12732,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K117" t="n">
@@ -12787,12 +12787,12 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K118" t="n">
@@ -12897,12 +12897,12 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K120" t="n">
@@ -12952,12 +12952,12 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K121" t="n">
@@ -13062,12 +13062,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K123" t="n">
@@ -13117,12 +13117,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K124" t="n">
@@ -13227,12 +13227,12 @@
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K126" t="n">
@@ -13282,12 +13282,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K127" t="n">
@@ -13337,12 +13337,12 @@
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K128" t="n">
@@ -13392,12 +13392,12 @@
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K129" t="n">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K130" t="n">
@@ -13502,12 +13502,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K131" t="n">
@@ -13557,12 +13557,12 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K132" t="n">
@@ -13722,12 +13722,12 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K135" t="n">
@@ -13777,12 +13777,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K136" t="n">
@@ -13832,12 +13832,12 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K137" t="n">
@@ -13887,12 +13887,12 @@
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K138" t="n">
@@ -13942,12 +13942,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K139" t="n">
@@ -13997,12 +13997,12 @@
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K140" t="n">
@@ -14052,12 +14052,12 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K141" t="n">
@@ -14162,12 +14162,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K143" t="n">
@@ -14217,12 +14217,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K144" t="n">
@@ -14272,12 +14272,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K145" t="n">
@@ -14327,12 +14327,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K146" t="n">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K148" t="n">
@@ -14492,12 +14492,12 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K149" t="n">
@@ -14547,12 +14547,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K150" t="n">
@@ -14602,12 +14602,12 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K151" t="n">
@@ -14657,12 +14657,12 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K152" t="n">
@@ -14712,12 +14712,12 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K153" t="n">
@@ -14822,12 +14822,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K155" t="n">
@@ -14877,12 +14877,12 @@
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K156" t="n">
@@ -14932,12 +14932,12 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K157" t="n">
@@ -14987,12 +14987,12 @@
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K158" t="n">
@@ -15097,12 +15097,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K160" t="n">
@@ -15262,12 +15262,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K163" t="n">
@@ -15317,12 +15317,12 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K164" t="n">
@@ -15372,12 +15372,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K165" t="n">
@@ -15482,12 +15482,12 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K167" t="n">
@@ -15647,12 +15647,12 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K170" t="n">
@@ -15812,12 +15812,12 @@
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>nova 15 Ultra SLY-AL00（12GB+512GB）幻夜黑</t>
+          <t>nova 15 Ultra SLY-AL00 （12GB+512GB）零度白</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>6942103183133</t>
+          <t>6942103183126</t>
         </is>
       </c>
       <c r="K173" t="n">
@@ -15867,12 +15867,12 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>nova 15 Ultra SLY-AL00 （12GB+512GB）零度白</t>
+          <t>nova 15 Ultra SLY-AL00（12GB+512GB）幻夜黑</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>6942103183126</t>
+          <t>6942103183133</t>
         </is>
       </c>
       <c r="K174" t="n">
@@ -15922,12 +15922,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K175" t="n">
@@ -15977,12 +15977,12 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 雪域白</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>6942103152702</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K176" t="n">
@@ -16032,12 +16032,12 @@
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K177" t="n">
@@ -16142,12 +16142,12 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 雪域白</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>6942103152726</t>
+          <t>6942103152702</t>
         </is>
       </c>
       <c r="K179" t="n">
@@ -16197,12 +16197,12 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
+          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>6942103153136</t>
+          <t>6942103142499</t>
         </is>
       </c>
       <c r="K180" t="n">
@@ -16362,12 +16362,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 云杉绿</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103153136</t>
         </is>
       </c>
       <c r="K183" t="n">
@@ -16417,12 +16417,12 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Mate 70 Pro 12GB+512GB 曜石黑</t>
+          <t>Mate 70 Pro PLR-AL00 12GB+512GB 风信紫</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>6942103142499</t>
+          <t>6942103152726</t>
         </is>
       </c>
       <c r="K184" t="n">
@@ -17362,17 +17362,17 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPhone 17&amp;17 Pro 钻石高清三强钢化玻璃膜 黑</t>
+          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 曜黑色</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>6922329935921</t>
+          <t>6955482542736</t>
         </is>
       </c>
       <c r="L9" t="n">
@@ -17433,17 +17433,17 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
+          <t>VOKAMO沃咔曼 iPhone 17&amp;17 Pro 钻石高清三强钢化玻璃膜 黑</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>6922329936560</t>
+          <t>6922329935921</t>
         </is>
       </c>
       <c r="L10" t="n">
@@ -17509,12 +17509,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>MAXCO美能格 RPB-W27 10000mAh 银河快充移动电源 曜黑色</t>
+          <t>VOKAMO沃咔曼 万马奔腾 45W 双口充电器 白色</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>6955482542736</t>
+          <t>6922329936560</t>
         </is>
       </c>
       <c r="L11" t="n">
@@ -17788,17 +17788,17 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>iPad Pro</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>11 英寸 iPad Pro 无线局域网机型 256GB 配标准玻璃面板 - 银色</t>
+          <t>MOCOLL摩可 iPad Pro 11英寸 铂金系列 高清钢化玻璃膜</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>195****95549</t>
+          <t>6937045847984</t>
         </is>
       </c>
       <c r="L15" t="n">
@@ -17859,17 +17859,17 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>耳机与扬声器</t>
+          <t>iPad Pro</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>RECCI锐思 REP W59 铂爵 ANC 头戴式无线耳机</t>
+          <t>11 英寸 iPad Pro 无线局域网机型 256GB 配标准玻璃面板 - 银色</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>6955482533109</t>
+          <t>195****95549</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -17930,17 +17930,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>创意工具</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iLink Pencil 智联系列电容手写笔</t>
+          <t>ZGA iPad 明派旋转系列保护皮套带笔槽</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>6922329934436</t>
+          <t>6927123805548</t>
         </is>
       </c>
       <c r="L17" t="n">
@@ -18001,17 +18001,17 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>支架</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>MOCOLL摩可 iPad Pro 11英寸 铂金系列 高清钢化玻璃膜</t>
+          <t>RECCI锐思 RHO-M23 折叠旋转 iPad 支架</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>6937045847984</t>
+          <t>6955482542989</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -18072,17 +18072,17 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>支架</t>
+          <t>创意工具</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>RECCI锐思 RHO-M23 折叠旋转 iPad 支架</t>
+          <t>VOKAMO沃咔曼 iLink Pencil 智联系列电容手写笔</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>6955482542989</t>
+          <t>6922329934436</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -18143,17 +18143,17 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>耳机与扬声器</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>ZGA iPad 明派旋转系列保护皮套带笔槽</t>
+          <t>RECCI锐思 REP W59 铂爵 ANC 头戴式无线耳机</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>6927123805548</t>
+          <t>6955482533109</t>
         </is>
       </c>
       <c r="L20" t="n">
@@ -18356,17 +18356,17 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>支架</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>MOCOLL摩可 铂金系列 iPad 高清钢化膜 11 英寸 iPad (A16) 透明</t>
+          <t>UGREEN绿联 iPad 旋转折叠平板支架 银色</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>6937045874478</t>
+          <t>6941876245338</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -18498,17 +18498,17 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>支架</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>UGREEN绿联 iPad 旋转折叠平板支架 银色</t>
+          <t>MOCOLL摩可 铂金系列 iPad 高清钢化膜 11 英寸 iPad (A16) 透明</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>6941876245338</t>
+          <t>6937045874478</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -18711,17 +18711,17 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>苹果电源</t>
+          <t>iPhone 17 Pro Max</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>20W USB-C 电源适配器-MWVW3CH/A</t>
+          <t>iPhone 17 Pro Max 512GB 深蓝色 - MG084CH/A</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>195****37103</t>
+          <t>195****41165</t>
         </is>
       </c>
       <c r="L28" t="n">
@@ -18782,17 +18782,17 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max</t>
+          <t>苹果电源</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>iPhone 17 Pro Max 512GB 深蓝色 - MG084CH/A</t>
+          <t>20W USB-C 电源适配器-MWVW3CH/A</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>195****41165</t>
+          <t>195****37103</t>
         </is>
       </c>
       <c r="L29" t="n">
@@ -18929,12 +18929,12 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>UGREEN绿联 USB-C PD 快充硅胶编织数据线 60W 1.5m</t>
+          <t>MOPHIE摩尔菲 45W 氮化镓快充头</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>6941876245444</t>
+          <t>840390349200</t>
         </is>
       </c>
       <c r="L31" t="n">
@@ -19000,12 +19000,12 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>MOPHIE摩尔菲 45W 氮化镓快充头</t>
+          <t>UGREEN绿联 USB-C PD 快充硅胶编织数据线 60W 1.5m</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>840390349200</t>
+          <t>6941876245444</t>
         </is>
       </c>
       <c r="L32" t="n">
@@ -19142,12 +19142,12 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>VOKAMO沃咔曼 iPhone 17系列 冰晶 AR 增透镜头保护膜 透明 三镜片</t>
+          <t>MOMAX摩米士 iPhone 17 Pro Max 空气防摔磁吸保护壳 太阳橙</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>6922329936034</t>
+          <t>4894222083837</t>
         </is>
       </c>
       <c r="L34" t="n">
@@ -19279,17 +19279,17 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>充电必备</t>
+          <t>保护壳及装备</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>MOPHIE摩尔菲 45W 氮化镓快充头</t>
+          <t>VOKAMO沃咔曼 iPhone 17系列 冰晶 AR 增透镜头保护膜 透明 三镜片</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>840390349200</t>
+          <t>6922329936034</t>
         </is>
       </c>
       <c r="L36" t="n">
@@ -19350,17 +19350,17 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>保护壳及装备</t>
+          <t>充电必备</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>MOMAX摩米士 iPhone 17 Pro Max 空气防摔磁吸保护壳 太阳橙</t>
+          <t>MOPHIE摩尔菲 45W 氮化镓快充头</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>4894222083837</t>
+          <t>840390349200</t>
         </is>
       </c>
       <c r="L37" t="n">
@@ -19421,17 +19421,17 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>购物袋</t>
+          <t>FPV</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>DJI 无纺布购物袋（中号）</t>
+          <t>DJI Neo 2（仅飞行器）</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>6937224129511</t>
+          <t>6937224131767</t>
         </is>
       </c>
       <c r="L38" t="n">
@@ -19492,17 +19492,17 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>FPV</t>
+          <t>购物袋</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>DJI Neo 2（仅飞行器）</t>
+          <t>DJI 无纺布购物袋（中号）</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>6937224131767</t>
+          <t>6937224129511</t>
         </is>
       </c>
       <c r="L39" t="n">
@@ -21828,12 +21828,12 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Pura X Max 典藏版 HOP-AL10(16GB+1TB) 幻夜黑</t>
+          <t>Pura X Max 典藏版 HOP-AL10(16GB+1TB) 零度白</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>6942103195419</t>
+          <t>6942103195433</t>
         </is>
       </c>
       <c r="L72" t="n">
@@ -21899,12 +21899,12 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Pura X Max 典藏版 HOP-AL10(16GB+1TB) 零度白</t>
+          <t>Pura X Max 典藏版 HOP-AL10(16GB+1TB) 幻夜黑</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>6942103195433</t>
+          <t>6942103195419</t>
         </is>
       </c>
       <c r="L73" t="n">
